--- a/data/trans_dic/IP42B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>La persona sustentadora principal recibe una pensión</t>
+          <t>La persona sustentadora principal recibe una pensión (tasa de respuesta: 28,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,35</t>
+          <t>0,0; 16,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 23,66</t>
+          <t>4,2; 22,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 16,3</t>
+          <t>1,5; 15,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,08</t>
+          <t>0,0; 11,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 19,68</t>
+          <t>4,57; 19,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 19,75</t>
+          <t>5,97; 21,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 9,71</t>
+          <t>1,12; 10,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 17,36</t>
+          <t>5,97; 18,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 15,87</t>
+          <t>5,59; 16,46</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 17,51</t>
+          <t>3,19; 18,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,14; 27,0</t>
+          <t>10,53; 28,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 14,07</t>
+          <t>3,64; 13,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 12,98</t>
+          <t>1,63; 13,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 19,27</t>
+          <t>5,55; 19,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 14,41</t>
+          <t>3,76; 14,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 12,84</t>
+          <t>3,22; 12,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 20,07</t>
+          <t>9,48; 20,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,94</t>
+          <t>4,55; 12,02</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 22,65</t>
+          <t>4,57; 23,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,27; 32,57</t>
+          <t>12,73; 30,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 17,86</t>
+          <t>3,92; 17,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 24,22</t>
+          <t>2,77; 24,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,63; 34,46</t>
+          <t>13,35; 35,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,32</t>
+          <t>1,21; 10,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 18,77</t>
+          <t>5,73; 19,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,34; 29,93</t>
+          <t>15,86; 30,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 10,97</t>
+          <t>3,21; 11,57</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 20,12</t>
+          <t>3,99; 21,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 23,65</t>
+          <t>5,27; 22,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 19,8</t>
+          <t>4,47; 18,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 19,12</t>
+          <t>5,11; 18,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 23,38</t>
+          <t>6,1; 23,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 13,54</t>
+          <t>2,16; 13,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 17,03</t>
+          <t>5,97; 16,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 19,87</t>
+          <t>7,77; 20,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 13,86</t>
+          <t>4,12; 12,85</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,94</t>
+          <t>5,59; 13,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,54; 20,23</t>
+          <t>11,22; 20,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 12,02</t>
+          <t>5,65; 12,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,93</t>
+          <t>4,31; 11,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 18,63</t>
+          <t>10,14; 18,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,64</t>
+          <t>5,11; 10,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,77</t>
+          <t>5,68; 10,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 17,86</t>
+          <t>12,05; 18,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,07</t>
+          <t>6,03; 10,32</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>La persona sustentadora principal recibe una pensión (tasa de respuesta: 28,99%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4366</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4171</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6809</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2861</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8538</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4331</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1543; 8390</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>607; 6418</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4768</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1948; 8371</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3597; 12671</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>746; 7125</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4739; 14455</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5619; 16546</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3929</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8371</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6923</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5112</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5984</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15293</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10212</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1327; 7818</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5126; 13638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2457; 9263</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>681; 5484</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3386; 11723</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2444; 9246</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2693; 10547</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10390; 22218</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6025; 15935</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3288</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9843</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4173</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9340</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6094</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>19184</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6186</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1329; 6977</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6024; 14474</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1765; 8022</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>724; 6350</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5365; 14134</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>623; 5490</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3162; 10862</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13881; 26721</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3101; 11171</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5644</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5024</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5959</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9322</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>11603</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8657</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1553; 8522</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2425; 10504</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2197; 9317</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2684; 9898</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2701; 10596</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1247; 7771</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5458; 15046</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7013; 18545</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4401; 13744</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>12496</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28224</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17029</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>24261</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>54618</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>34596</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>7602; 18744</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20048; 36695</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11426; 24573</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6922; 17956</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19076; 35275</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>11986; 24817</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16854; 32322</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>44175; 66638</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>26344; 45078</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP42B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,37</t>
+          <t>0,0; 16,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 22,86</t>
+          <t>4,84; 23,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 15,91</t>
+          <t>1,72; 16,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,85</t>
+          <t>0,0; 12,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 19,64</t>
+          <t>3,32; 19,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 21,05</t>
+          <t>5,81; 20,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,68</t>
+          <t>1,0; 10,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 18,22</t>
+          <t>5,95; 18,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 16,46</t>
+          <t>4,98; 14,99</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 18,8</t>
+          <t>4,61; 18,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 28,03</t>
+          <t>9,92; 27,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,72</t>
+          <t>2,95; 13,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 13,09</t>
+          <t>1,63; 13,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 19,23</t>
+          <t>6,08; 20,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 14,22</t>
+          <t>3,77; 14,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 12,63</t>
+          <t>3,19; 12,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 20,26</t>
+          <t>9,17; 19,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 12,02</t>
+          <t>4,77; 11,94</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 23,99</t>
+          <t>4,52; 23,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 30,57</t>
+          <t>12,31; 31,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 17,81</t>
+          <t>4,04; 16,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 24,32</t>
+          <t>2,77; 23,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,35; 35,18</t>
+          <t>14,32; 36,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,65</t>
+          <t>1,23; 10,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 19,68</t>
+          <t>5,09; 19,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,86; 30,53</t>
+          <t>15,39; 29,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,57</t>
+          <t>3,25; 11,07</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 21,91</t>
+          <t>3,87; 20,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 22,83</t>
+          <t>4,93; 23,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 18,95</t>
+          <t>4,43; 19,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 18,83</t>
+          <t>5,03; 18,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 23,94</t>
+          <t>7,17; 23,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 13,45</t>
+          <t>2,3; 13,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 16,45</t>
+          <t>5,58; 16,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 20,55</t>
+          <t>7,85; 19,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 12,85</t>
+          <t>4,59; 13,64</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 13,78</t>
+          <t>5,84; 13,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 20,53</t>
+          <t>11,87; 20,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 12,16</t>
+          <t>6,03; 12,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,17</t>
+          <t>4,26; 10,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,14; 18,76</t>
+          <t>10,34; 18,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,58</t>
+          <t>4,91; 10,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,89</t>
+          <t>5,84; 11,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,05; 18,17</t>
+          <t>11,94; 18,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,32</t>
+          <t>6,01; 10,41</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4331</t>
+          <t>0; 4285</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1543; 8390</t>
+          <t>1775; 8653</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>607; 6418</t>
+          <t>694; 6517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4768</t>
+          <t>0; 4942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1948; 8371</t>
+          <t>1414; 8171</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3597; 12671</t>
+          <t>3495; 12104</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>746; 7125</t>
+          <t>665; 7112</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4739; 14455</t>
+          <t>4717; 14404</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5619; 16546</t>
+          <t>5009; 15071</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1327; 7818</t>
+          <t>1916; 7779</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5126; 13638</t>
+          <t>4827; 13274</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2457; 9263</t>
+          <t>1994; 9195</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>681; 5484</t>
+          <t>682; 5482</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3386; 11723</t>
+          <t>3707; 12421</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2444; 9246</t>
+          <t>2449; 9538</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2693; 10547</t>
+          <t>2664; 10238</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10390; 22218</t>
+          <t>10049; 21590</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6025; 15935</t>
+          <t>6328; 15827</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1329; 6977</t>
+          <t>1315; 6828</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6024; 14474</t>
+          <t>5828; 14898</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1765; 8022</t>
+          <t>1819; 7431</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>724; 6350</t>
+          <t>724; 6264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5365; 14134</t>
+          <t>5754; 14477</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>623; 5490</t>
+          <t>632; 5566</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3162; 10862</t>
+          <t>2812; 10793</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13881; 26721</t>
+          <t>13466; 25793</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3101; 11171</t>
+          <t>3144; 10689</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1553; 8522</t>
+          <t>1505; 7946</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2425; 10504</t>
+          <t>2267; 10823</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2197; 9317</t>
+          <t>2180; 9570</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2684; 9898</t>
+          <t>2641; 9618</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2701; 10596</t>
+          <t>3173; 10475</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1247; 7771</t>
+          <t>1330; 8076</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5458; 15046</t>
+          <t>5100; 14938</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7013; 18545</t>
+          <t>7087; 17353</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4401; 13744</t>
+          <t>4913; 14584</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7602; 18744</t>
+          <t>7944; 18363</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20048; 36695</t>
+          <t>21221; 37511</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11426; 24573</t>
+          <t>12180; 24540</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6922; 17956</t>
+          <t>6845; 17396</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19076; 35275</t>
+          <t>19449; 35299</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11986; 24817</t>
+          <t>11510; 25294</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16854; 32322</t>
+          <t>17329; 33111</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>44175; 66638</t>
+          <t>43786; 66645</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26344; 45078</t>
+          <t>26230; 45458</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP42B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,79%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11,89%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,77%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,19</t>
+          <t>0,0; 13,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 23,57</t>
+          <t>3,66; 19,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 16,15</t>
+          <t>5,94; 19,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,28</t>
+          <t>0,0; 16,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 19,17</t>
+          <t>4,08; 23,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 20,11</t>
+          <t>1,94; 16,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,66</t>
+          <t>1,13; 9,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 18,16</t>
+          <t>6,16; 17,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 14,99</t>
+          <t>5,37; 15,87</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,45%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>17,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,55%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 18,7</t>
+          <t>1,63; 12,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 27,28</t>
+          <t>5,72; 19,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 13,62</t>
+          <t>3,8; 14,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 13,08</t>
+          <t>3,18; 17,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 20,37</t>
+          <t>10,14; 27,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 14,67</t>
+          <t>3,54; 14,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 12,26</t>
+          <t>3,21; 12,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,17; 19,69</t>
+          <t>9,57; 20,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,94</t>
+          <t>4,36; 11,94</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,75%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11,3%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>20,79%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,26%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 23,48</t>
+          <t>2,78; 24,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,31; 31,47</t>
+          <t>13,63; 34,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 16,5</t>
+          <t>1,21; 10,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 23,99</t>
+          <t>4,46; 22,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,32; 36,03</t>
+          <t>13,27; 32,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,8</t>
+          <t>4,24; 17,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 19,55</t>
+          <t>5,06; 18,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,39; 29,47</t>
+          <t>15,34; 29,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,07</t>
+          <t>3,14; 10,97</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>10,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>12,27%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,22%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 20,43</t>
+          <t>5,15; 19,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 23,53</t>
+          <t>7,3; 23,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 19,47</t>
+          <t>2,04; 13,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 18,3</t>
+          <t>3,53; 20,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 23,67</t>
+          <t>5,37; 23,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 13,97</t>
+          <t>4,4; 19,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 16,34</t>
+          <t>5,97; 17,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,85; 19,23</t>
+          <t>7,71; 19,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 13,64</t>
+          <t>4,6; 13,86</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>9,19%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>15,79%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,43%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 13,5</t>
+          <t>4,37; 10,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,87; 20,99</t>
+          <t>10,09; 18,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,14</t>
+          <t>4,81; 10,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,82</t>
+          <t>5,52; 13,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 18,77</t>
+          <t>11,54; 20,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 10,78</t>
+          <t>5,69; 12,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,15</t>
+          <t>5,83; 10,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,94; 18,17</t>
+          <t>11,98; 17,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,41</t>
+          <t>5,96; 10,07</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1321,22 +1321,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4171</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6809</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1392</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>4366</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2732</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1468</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4171</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6809</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4285</t>
+          <t>0; 5262</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1775; 8653</t>
+          <t>1558; 8388</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>694; 6517</t>
+          <t>3577; 11892</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4942</t>
+          <t>0; 4327</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1414; 8171</t>
+          <t>1499; 8683</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3495; 12104</t>
+          <t>782; 6575</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>665; 7112</t>
+          <t>754; 6476</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4717; 14404</t>
+          <t>4890; 13770</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5009; 15071</t>
+          <t>5395; 15958</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6923</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5112</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3929</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8371</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5101</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6923</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5112</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1916; 7779</t>
+          <t>681; 5439</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4827; 13274</t>
+          <t>3487; 11750</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1994; 9195</t>
+          <t>2471; 9366</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>682; 5482</t>
+          <t>1324; 7284</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3707; 12421</t>
+          <t>4937; 13136</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2449; 9538</t>
+          <t>2393; 9498</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2664; 10238</t>
+          <t>2678; 10719</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10049; 21590</t>
+          <t>10493; 22002</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6328; 15827</t>
+          <t>5778; 15817</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9340</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>3288</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>9843</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4173</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2806</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9340</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1315; 6828</t>
+          <t>725; 6324</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5828; 14898</t>
+          <t>5478; 13845</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1819; 7431</t>
+          <t>623; 5319</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>724; 6264</t>
+          <t>1298; 6588</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5754; 14477</t>
+          <t>6284; 15418</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>632; 5566</t>
+          <t>1910; 8043</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2812; 10793</t>
+          <t>2795; 10360</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13466; 25793</t>
+          <t>13426; 26192</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3144; 10689</t>
+          <t>3035; 10594</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5959</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>5644</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5024</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5435</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5959</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3634</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1505; 7946</t>
+          <t>2708; 10046</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2267; 10823</t>
+          <t>3231; 10344</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2180; 9570</t>
+          <t>1179; 7826</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2641; 9618</t>
+          <t>1372; 7826</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3173; 10475</t>
+          <t>2468; 10877</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1330; 8076</t>
+          <t>2162; 9734</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5100; 14938</t>
+          <t>5457; 15573</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7087; 17353</t>
+          <t>6955; 17932</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4913; 14584</t>
+          <t>4915; 14821</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>12496</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>28224</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>17029</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>26394</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17567</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7944; 18363</t>
+          <t>7026; 17578</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21221; 37511</t>
+          <t>18970; 35036</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12180; 24540</t>
+          <t>11284; 24965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6845; 17396</t>
+          <t>7509; 18963</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19449; 35299</t>
+          <t>20630; 36151</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11510; 25294</t>
+          <t>11500; 24287</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17329; 33111</t>
+          <t>17297; 31965</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>43786; 66645</t>
+          <t>43936; 65513</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26230; 45458</t>
+          <t>26016; 43951</t>
         </is>
       </c>
     </row>
